--- a/data/processed/data_processed_occurences_20250704.xlsx
+++ b/data/processed/data_processed_occurences_20250704.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B198"/>
+  <dimension ref="A1:B197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1869,297 +1869,297 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Silene</t>
+          <t>Silene latifolia</t>
         </is>
       </c>
       <c r="B152">
-        <v>5</v>
+        <v>155</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Silene latifolia</t>
+          <t>Silene vulgaris</t>
         </is>
       </c>
       <c r="B153">
-        <v>149</v>
+        <v>199</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Silene vulgaris</t>
+          <t>Silphium terebinthinaceum</t>
         </is>
       </c>
       <c r="B154">
-        <v>199</v>
+        <v>90</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Silphium terebinthinaceum</t>
+          <t>Solanum americanum</t>
         </is>
       </c>
       <c r="B155">
-        <v>91</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Solanum americanum</t>
+          <t>Solanum carolinense</t>
         </is>
       </c>
       <c r="B156">
-        <v>12</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Solanum carolinense</t>
+          <t>Solidago</t>
         </is>
       </c>
       <c r="B157">
-        <v>321</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Solidago</t>
+          <t>Solidago altissima</t>
         </is>
       </c>
       <c r="B158">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Solidago altissima</t>
+          <t>Solidago canadensis</t>
         </is>
       </c>
       <c r="B159">
-        <v>4</v>
+        <v>171</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Solidago canadensis</t>
+          <t>Solidago juncea</t>
         </is>
       </c>
       <c r="B160">
-        <v>171</v>
+        <v>54</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Solidago juncea</t>
+          <t>Solidago nemoralis</t>
         </is>
       </c>
       <c r="B161">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Solidago nemoralis</t>
+          <t>Solidago rigida</t>
         </is>
       </c>
       <c r="B162">
-        <v>57</v>
+        <v>151</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Solidago rigida</t>
+          <t>Solidago speciosa</t>
         </is>
       </c>
       <c r="B163">
-        <v>151</v>
+        <v>75</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Solidago speciosa</t>
+          <t>Sorghastrum nutans</t>
         </is>
       </c>
       <c r="B164">
-        <v>75</v>
+        <v>158</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sorghastrum nutans</t>
+          <t>Sporobolus cryptandrus</t>
         </is>
       </c>
       <c r="B165">
-        <v>158</v>
+        <v>196</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sporobolus cryptandrus</t>
+          <t>Stellaria media</t>
         </is>
       </c>
       <c r="B166">
-        <v>196</v>
+        <v>115</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Stellaria media</t>
+          <t>Symphyotrichum</t>
         </is>
       </c>
       <c r="B167">
-        <v>115</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Symphyotrichum</t>
+          <t>Symphyotrichum ericoides</t>
         </is>
       </c>
       <c r="B168">
-        <v>2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Symphyotrichum ericoides</t>
+          <t>Symphyotrichum laeve</t>
         </is>
       </c>
       <c r="B169">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Symphyotrichum laeve</t>
+          <t>Symphyotrichum lanceolatum</t>
         </is>
       </c>
       <c r="B170">
-        <v>93</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Symphyotrichum lanceolatum</t>
+          <t>Symphyotrichum oolentangiense</t>
         </is>
       </c>
       <c r="B171">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Symphyotrichum oolentangiense</t>
+          <t>Symphyotrichum pilosum</t>
         </is>
       </c>
       <c r="B172">
-        <v>54</v>
+        <v>135</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Symphyotrichum pilosum</t>
+          <t>Symphyotrichum undulatum</t>
         </is>
       </c>
       <c r="B173">
-        <v>135</v>
+        <v>162</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Symphyotrichum undulatum</t>
+          <t>Taraxacum officinale</t>
         </is>
       </c>
       <c r="B174">
-        <v>162</v>
+        <v>39</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Taraxacum officinale</t>
+          <t>Toxicodendron radicans</t>
         </is>
       </c>
       <c r="B175">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Toxicodendron radicans</t>
+          <t>Tradescantia ohiensis</t>
         </is>
       </c>
       <c r="B176">
-        <v>29</v>
+        <v>54</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Tradescantia ohiensis</t>
+          <t>Tragopogon</t>
         </is>
       </c>
       <c r="B177">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Tragopogon</t>
+          <t>Trifolium</t>
         </is>
       </c>
       <c r="B178">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Trifolium</t>
+          <t>Trifolium arvense</t>
         </is>
       </c>
       <c r="B179">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Trifolium arvense</t>
+          <t>Trifolium campestre</t>
         </is>
       </c>
       <c r="B180">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Trifolium campestre</t>
+          <t>Trifolium dubium</t>
         </is>
       </c>
       <c r="B181">
@@ -2169,7 +2169,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Trifolium dubium</t>
+          <t>Trifolium hybridum</t>
         </is>
       </c>
       <c r="B182">
@@ -2179,160 +2179,150 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Trifolium hybridum</t>
+          <t>Trifolium pratense</t>
         </is>
       </c>
       <c r="B183">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Trifolium pratense</t>
+          <t>Trifolium repens</t>
         </is>
       </c>
       <c r="B184">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Trifolium repens</t>
+          <t>Turritis glabra</t>
         </is>
       </c>
       <c r="B185">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Turritis glabra</t>
+          <t>Ulmus</t>
         </is>
       </c>
       <c r="B186">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Ulmus</t>
+          <t>Urtica dioica</t>
         </is>
       </c>
       <c r="B187">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Urtica dioica</t>
+          <t>Verbascum thapsus</t>
         </is>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>218</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Verbascum thapsus</t>
+          <t>Verbena</t>
         </is>
       </c>
       <c r="B189">
-        <v>218</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Verbena</t>
+          <t>Verbena stricta</t>
         </is>
       </c>
       <c r="B190">
-        <v>10</v>
+        <v>230</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Verbena stricta</t>
+          <t>Verbena urticifolia</t>
         </is>
       </c>
       <c r="B191">
-        <v>230</v>
+        <v>34</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Verbena urticifolia</t>
+          <t>Vicia</t>
         </is>
       </c>
       <c r="B192">
-        <v>34</v>
+        <v>137</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Vicia</t>
+          <t>Vinca</t>
         </is>
       </c>
       <c r="B193">
-        <v>137</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Vinca</t>
+          <t>Viola</t>
         </is>
       </c>
       <c r="B194">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Viola</t>
+          <t>Vitis</t>
         </is>
       </c>
       <c r="B195">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Vitis</t>
+          <t>Zizia aptera</t>
         </is>
       </c>
       <c r="B196">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Zizia aptera</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="B197">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="B198">
         <v>58</v>
       </c>
     </row>

--- a/data/processed/data_processed_occurences_20250704.xlsx
+++ b/data/processed/data_processed_occurences_20250704.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B197"/>
+  <dimension ref="A1:B198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -739,27 +739,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cistus lasianthus subsp. alyssoides</t>
+          <t>Coreopsis lanceolata</t>
         </is>
       </c>
       <c r="B39">
-        <v>78</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Coreopsis lanceolata</t>
+          <t>Cyperaceae</t>
         </is>
       </c>
       <c r="B40">
-        <v>370</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cyperaceae</t>
+          <t>Cyperus</t>
         </is>
       </c>
       <c r="B41">
@@ -769,401 +769,401 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cyperus</t>
+          <t>Cyperus lupulinus</t>
         </is>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cyperus lupulinus</t>
+          <t>Dactylis glomerata</t>
         </is>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dactylis glomerata</t>
+          <t>Dalea purpurea</t>
         </is>
       </c>
       <c r="B44">
-        <v>25</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dalea purpurea</t>
+          <t>Danthonia spicata</t>
         </is>
       </c>
       <c r="B45">
-        <v>242</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Danthonia spicata</t>
+          <t>Daucus carota</t>
         </is>
       </c>
       <c r="B46">
-        <v>9</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Daucus carota</t>
+          <t>Desmodium</t>
         </is>
       </c>
       <c r="B47">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Desmodium</t>
+          <t>Desmodium canadense</t>
         </is>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Desmodium canadense</t>
+          <t>Desmodium illinoense</t>
         </is>
       </c>
       <c r="B49">
-        <v>45</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Desmodium illinoense</t>
+          <t>Desmodium paniculatum</t>
         </is>
       </c>
       <c r="B50">
-        <v>112</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Desmodium paniculatum</t>
+          <t>Dichanthelium</t>
         </is>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dichanthelium</t>
+          <t>Digitaria</t>
         </is>
       </c>
       <c r="B52">
-        <v>81</v>
+        <v>607</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Digitaria</t>
+          <t>Drymocallis arguta</t>
         </is>
       </c>
       <c r="B53">
-        <v>607</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Drymocallis arguta</t>
+          <t>Echinacea pallida</t>
         </is>
       </c>
       <c r="B54">
-        <v>241</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Echinacea pallida</t>
+          <t>Echinacea purpurea</t>
         </is>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>281</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Echinacea purpurea</t>
+          <t>Elaeagnus umbellata</t>
         </is>
       </c>
       <c r="B56">
-        <v>281</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Elaeagnus umbellata</t>
+          <t>Elymus</t>
         </is>
       </c>
       <c r="B57">
-        <v>14</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Elymus</t>
+          <t>Elymus canadensis</t>
         </is>
       </c>
       <c r="B58">
-        <v>135</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Elymus canadensis</t>
+          <t>Elymus repens</t>
         </is>
       </c>
       <c r="B59">
-        <v>177</v>
+        <v>356</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Elymus repens</t>
+          <t>Elymus virginicus</t>
         </is>
       </c>
       <c r="B60">
-        <v>356</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Elymus virginicus</t>
+          <t>Eragrostis cilianensis</t>
         </is>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Eragrostis cilianensis</t>
+          <t>Eragrostis spectabilis</t>
         </is>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Eragrostis spectabilis</t>
+          <t>Erechtites hieraciifolius</t>
         </is>
       </c>
       <c r="B63">
-        <v>87</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Erechtites hieraciifolius</t>
+          <t>Erigeron</t>
         </is>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Erigeron</t>
+          <t>Erigeron canadensis</t>
         </is>
       </c>
       <c r="B65">
-        <v>262</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Erigeron canadensis</t>
+          <t>Eryngium yuccifolium</t>
         </is>
       </c>
       <c r="B66">
-        <v>292</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Eryngium yuccifolium</t>
+          <t>Euphorbia maculata</t>
         </is>
       </c>
       <c r="B67">
-        <v>163</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Euphorbia maculata</t>
+          <t>Euthamia graminifolia</t>
         </is>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Euthamia graminifolia</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="B69">
-        <v>126</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
+          <t>Fagopyrum esculentum</t>
         </is>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Fagopyrum esculentum</t>
+          <t>Fallopia convolvulus</t>
         </is>
       </c>
       <c r="B71">
-        <v>11</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fallopia convolvulus</t>
+          <t>Festuca rubra</t>
         </is>
       </c>
       <c r="B72">
-        <v>53</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Festuca rubra</t>
+          <t>Festuca trachyphylla</t>
         </is>
       </c>
       <c r="B73">
-        <v>112</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Festuca trachyphylla</t>
+          <t>Gamochaeta purpurea</t>
         </is>
       </c>
       <c r="B74">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gamochaeta purpurea</t>
+          <t>Geranium</t>
         </is>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Geranium</t>
+          <t>Geum canadense</t>
         </is>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Geum canadense</t>
+          <t>Gleditsia triacanthos</t>
         </is>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gleditsia triacanthos</t>
+          <t>Gnaphalium</t>
         </is>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gnaphalium</t>
+          <t>Gnaphalium uliginosum</t>
         </is>
       </c>
       <c r="B79">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Gnaphalium uliginosum</t>
+          <t>Hackelia virginiana</t>
         </is>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Hackelia virginiana</t>
+          <t>Helianthus occidentalis</t>
         </is>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82">
@@ -1649,7 +1649,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Potentilla anserina</t>
+          <t>Potentilla argentea</t>
         </is>
       </c>
       <c r="B130">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="B169">
-        <v>93</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -2324,6 +2324,11 @@
       </c>
       <c r="B197">
         <v>58</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/data_processed_occurences_20250704.xlsx
+++ b/data/processed/data_processed_occurences_20250704.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B198"/>
+  <dimension ref="A1:B196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -819,147 +819,147 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Desmodium</t>
+          <t>Desmodium illinoense</t>
         </is>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Desmodium canadense</t>
+          <t>Desmodium paniculatum</t>
         </is>
       </c>
       <c r="B48">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Desmodium illinoense</t>
+          <t>Dichanthelium</t>
         </is>
       </c>
       <c r="B49">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Desmodium paniculatum</t>
+          <t>Digitaria</t>
         </is>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>607</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dichanthelium</t>
+          <t>Drymocallis arguta</t>
         </is>
       </c>
       <c r="B51">
-        <v>81</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Digitaria</t>
+          <t>Echinacea pallida</t>
         </is>
       </c>
       <c r="B52">
-        <v>607</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Drymocallis arguta</t>
+          <t>Echinacea purpurea</t>
         </is>
       </c>
       <c r="B53">
-        <v>241</v>
+        <v>281</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Echinacea pallida</t>
+          <t>Elaeagnus umbellata</t>
         </is>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Echinacea purpurea</t>
+          <t>Elymus</t>
         </is>
       </c>
       <c r="B55">
-        <v>281</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Elaeagnus umbellata</t>
+          <t>Elymus canadensis</t>
         </is>
       </c>
       <c r="B56">
-        <v>14</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Elymus</t>
+          <t>Elymus repens</t>
         </is>
       </c>
       <c r="B57">
-        <v>135</v>
+        <v>356</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Elymus canadensis</t>
+          <t>Elymus virginicus</t>
         </is>
       </c>
       <c r="B58">
-        <v>177</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Elymus repens</t>
+          <t>Eragrostis cilianensis</t>
         </is>
       </c>
       <c r="B59">
-        <v>356</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Elymus virginicus</t>
+          <t>Eragrostis spectabilis</t>
         </is>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Eragrostis cilianensis</t>
+          <t>Erechtites hieraciifolius</t>
         </is>
       </c>
       <c r="B61">
@@ -969,137 +969,137 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Eragrostis spectabilis</t>
+          <t>Erigeron</t>
         </is>
       </c>
       <c r="B62">
-        <v>87</v>
+        <v>262</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Erechtites hieraciifolius</t>
+          <t>Erigeron canadensis</t>
         </is>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Erigeron</t>
+          <t>Eryngium yuccifolium</t>
         </is>
       </c>
       <c r="B64">
-        <v>262</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Erigeron canadensis</t>
+          <t>Euphorbia maculata</t>
         </is>
       </c>
       <c r="B65">
-        <v>292</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Eryngium yuccifolium</t>
+          <t>Euthamia graminifolia</t>
         </is>
       </c>
       <c r="B66">
-        <v>163</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Euphorbia maculata</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Euthamia graminifolia</t>
+          <t>Fagopyrum esculentum</t>
         </is>
       </c>
       <c r="B68">
-        <v>126</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
+          <t>Fallopia convolvulus</t>
         </is>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fagopyrum esculentum</t>
+          <t>Festuca rubra</t>
         </is>
       </c>
       <c r="B70">
-        <v>11</v>
+        <v>112</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Fallopia convolvulus</t>
+          <t>Festuca trachyphylla</t>
         </is>
       </c>
       <c r="B71">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Festuca rubra</t>
+          <t>Gamochaeta purpurea</t>
         </is>
       </c>
       <c r="B72">
-        <v>112</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Festuca trachyphylla</t>
+          <t>Geranium</t>
         </is>
       </c>
       <c r="B73">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Gamochaeta purpurea</t>
+          <t>Geum canadense</t>
         </is>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Geranium</t>
+          <t>Gleditsia triacanthos</t>
         </is>
       </c>
       <c r="B75">
@@ -1109,17 +1109,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Geum canadense</t>
+          <t>Gnaphalium</t>
         </is>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Gleditsia triacanthos</t>
+          <t>Gnaphalium uliginosum</t>
         </is>
       </c>
       <c r="B77">
@@ -1129,197 +1129,197 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gnaphalium</t>
+          <t>Hackelia virginiana</t>
         </is>
       </c>
       <c r="B78">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gnaphalium uliginosum</t>
+          <t>Helianthus occidentalis</t>
         </is>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Hackelia virginiana</t>
+          <t>Hieracium</t>
         </is>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Helianthus occidentalis</t>
+          <t>Hypericum perforatum</t>
         </is>
       </c>
       <c r="B81">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hieracium</t>
+          <t>Hypochaeris radicata</t>
         </is>
       </c>
       <c r="B82">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Hypericum perforatum</t>
+          <t>Juncus effusus</t>
         </is>
       </c>
       <c r="B83">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Hypochaeris radicata</t>
+          <t>Juncus tenuis</t>
         </is>
       </c>
       <c r="B84">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Juncus effusus</t>
+          <t>Koeleria macrantha</t>
         </is>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Juncus tenuis</t>
+          <t>Krigia</t>
         </is>
       </c>
       <c r="B86">
-        <v>113</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Koeleria macrantha</t>
+          <t>Lactuca</t>
         </is>
       </c>
       <c r="B87">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Krigia</t>
+          <t>Lepidium campestre</t>
         </is>
       </c>
       <c r="B88">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Lactuca</t>
+          <t>Lespedeza capitata</t>
         </is>
       </c>
       <c r="B89">
-        <v>4</v>
+        <v>286</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lepidium campestre</t>
+          <t>Lespedeza hirta</t>
         </is>
       </c>
       <c r="B90">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lespedeza capitata</t>
+          <t>Lespedeza virginica</t>
         </is>
       </c>
       <c r="B91">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Lespedeza hirta</t>
+          <t>Liatris cylindracea</t>
         </is>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Lespedeza virginica</t>
+          <t>Lonicera maackii</t>
         </is>
       </c>
       <c r="B93">
-        <v>262</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Liatris cylindracea</t>
+          <t>Lupinus perennis</t>
         </is>
       </c>
       <c r="B94">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lonicera maackii</t>
+          <t>Malus</t>
         </is>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Lupinus perennis</t>
+          <t>Malva neglecta</t>
         </is>
       </c>
       <c r="B96">
-        <v>55</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Malus</t>
+          <t>Medicago</t>
         </is>
       </c>
       <c r="B97">
@@ -1329,507 +1329,507 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Malva neglecta</t>
+          <t>Medicago lupulina</t>
         </is>
       </c>
       <c r="B98">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Medicago</t>
+          <t>Medicago sativa</t>
         </is>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Medicago lupulina</t>
+          <t>Melilotus</t>
         </is>
       </c>
       <c r="B100">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Medicago sativa</t>
+          <t>Mollugo verticillata</t>
         </is>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Melilotus</t>
+          <t>Monarda fistulosa</t>
         </is>
       </c>
       <c r="B102">
-        <v>47</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Mollugo verticillata</t>
+          <t>Monarda punctata</t>
         </is>
       </c>
       <c r="B103">
-        <v>97</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Monarda fistulosa</t>
+          <t>Morus alba</t>
         </is>
       </c>
       <c r="B104">
-        <v>267</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Monarda punctata</t>
+          <t>Morus rubra</t>
         </is>
       </c>
       <c r="B105">
-        <v>206</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Morus alba</t>
+          <t>Oenothera</t>
         </is>
       </c>
       <c r="B106">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Morus rubra</t>
+          <t>Oenothera biennis</t>
         </is>
       </c>
       <c r="B107">
-        <v>9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Oenothera</t>
+          <t>Oxalis stricta</t>
         </is>
       </c>
       <c r="B108">
-        <v>5</v>
+        <v>298</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Oenothera biennis</t>
+          <t>Panicum</t>
         </is>
       </c>
       <c r="B109">
-        <v>55</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Oxalis stricta</t>
+          <t>Panicum capillare</t>
         </is>
       </c>
       <c r="B110">
-        <v>298</v>
+        <v>190</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Panicum</t>
+          <t>Panicum dichotomiflorum</t>
         </is>
       </c>
       <c r="B111">
-        <v>4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Panicum capillare</t>
+          <t>Panicum virgatum</t>
         </is>
       </c>
       <c r="B112">
-        <v>190</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Panicum dichotomiflorum</t>
+          <t>Paspalum setaceum</t>
         </is>
       </c>
       <c r="B113">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Panicum virgatum</t>
+          <t>Penstemon digitalis</t>
         </is>
       </c>
       <c r="B114">
-        <v>378</v>
+        <v>260</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Paspalum setaceum</t>
+          <t>Penstemon hirsutus</t>
         </is>
       </c>
       <c r="B115">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Penstemon digitalis</t>
+          <t>Persicaria maculosa</t>
         </is>
       </c>
       <c r="B116">
-        <v>260</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Penstemon hirsutus</t>
+          <t>Phleum pratense</t>
         </is>
       </c>
       <c r="B117">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Persicaria maculosa</t>
+          <t>Phytolacca</t>
         </is>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Phleum pratense</t>
+          <t>Phytolacca americana</t>
         </is>
       </c>
       <c r="B119">
-        <v>5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Phytolacca</t>
+          <t>Phytolacca heterotepala</t>
         </is>
       </c>
       <c r="B120">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Phytolacca americana</t>
+          <t>Plantago lanceolata</t>
         </is>
       </c>
       <c r="B121">
-        <v>68</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Phytolacca heterotepala</t>
+          <t>Plantago major</t>
         </is>
       </c>
       <c r="B122">
-        <v>83</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Plantago lanceolata</t>
+          <t>Poa</t>
         </is>
       </c>
       <c r="B123">
-        <v>378</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Plantago major</t>
+          <t>Poa annua</t>
         </is>
       </c>
       <c r="B124">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Poa</t>
+          <t>Poa compressa</t>
         </is>
       </c>
       <c r="B125">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Poa annua</t>
+          <t>Poa pratensis</t>
         </is>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>345</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Poa compressa</t>
+          <t>Poaceae</t>
         </is>
       </c>
       <c r="B127">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Poa pratensis</t>
+          <t>Potentilla argentea</t>
         </is>
       </c>
       <c r="B128">
-        <v>345</v>
+        <v>100</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Poaceae</t>
+          <t>Potentilla norvegica</t>
         </is>
       </c>
       <c r="B129">
-        <v>89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Potentilla argentea</t>
+          <t>Potentilla recta</t>
         </is>
       </c>
       <c r="B130">
-        <v>100</v>
+        <v>67</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Potentilla norvegica</t>
+          <t>Potentilla simplex</t>
         </is>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Potentilla recta</t>
+          <t>Prunus</t>
         </is>
       </c>
       <c r="B132">
-        <v>67</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Potentilla simplex</t>
+          <t>Prunus serotina</t>
         </is>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Prunus</t>
+          <t>Pseudognaphalium obtusifolium</t>
         </is>
       </c>
       <c r="B134">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Prunus serotina</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="B135">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Pseudognaphalium obtusifolium</t>
+          <t>Quercus velutina</t>
         </is>
       </c>
       <c r="B136">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Ratibida pinnata</t>
         </is>
       </c>
       <c r="B137">
-        <v>4</v>
+        <v>440</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Quercus velutina</t>
+          <t>Rhus</t>
         </is>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ratibida pinnata</t>
+          <t>Rubus allegheniensis</t>
         </is>
       </c>
       <c r="B139">
-        <v>440</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Rhus</t>
+          <t>Rubus flagellaris</t>
         </is>
       </c>
       <c r="B140">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Rubus allegheniensis</t>
+          <t>Rubus occidentalis</t>
         </is>
       </c>
       <c r="B141">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Rubus flagellaris</t>
+          <t>Rudbeckia hirta</t>
         </is>
       </c>
       <c r="B142">
-        <v>42</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Rubus occidentalis</t>
+          <t>Rumex acetosa</t>
         </is>
       </c>
       <c r="B143">
-        <v>3</v>
+        <v>190</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Rudbeckia hirta</t>
+          <t>Rumex acetosella</t>
         </is>
       </c>
       <c r="B144">
-        <v>272</v>
+        <v>51</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Rumex acetosa</t>
+          <t>Rumex crispus</t>
         </is>
       </c>
       <c r="B145">
-        <v>190</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Rumex acetosella</t>
+          <t>Rumex obtusifolius</t>
         </is>
       </c>
       <c r="B146">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Rumex crispus</t>
+          <t>Schizachyrium scoparium</t>
         </is>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>468</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Rumex obtusifolius</t>
+          <t>Scrophularia lanceolata</t>
         </is>
       </c>
       <c r="B148">
@@ -1839,317 +1839,317 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Schizachyrium scoparium</t>
+          <t>Setaria</t>
         </is>
       </c>
       <c r="B149">
-        <v>468</v>
+        <v>56</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Scrophularia lanceolata</t>
+          <t>Silene latifolia</t>
         </is>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>155</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Setaria</t>
+          <t>Silene vulgaris</t>
         </is>
       </c>
       <c r="B151">
-        <v>56</v>
+        <v>199</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Silene latifolia</t>
+          <t>Silphium terebinthinaceum</t>
         </is>
       </c>
       <c r="B152">
-        <v>155</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Silene vulgaris</t>
+          <t>Solanum americanum</t>
         </is>
       </c>
       <c r="B153">
-        <v>199</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Silphium terebinthinaceum</t>
+          <t>Solanum carolinense</t>
         </is>
       </c>
       <c r="B154">
-        <v>90</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Solanum americanum</t>
+          <t>Solidago</t>
         </is>
       </c>
       <c r="B155">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Solanum carolinense</t>
+          <t>Solidago altissima</t>
         </is>
       </c>
       <c r="B156">
-        <v>321</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Solidago</t>
+          <t>Solidago canadensis</t>
         </is>
       </c>
       <c r="B157">
-        <v>8</v>
+        <v>171</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Solidago altissima</t>
+          <t>Solidago juncea</t>
         </is>
       </c>
       <c r="B158">
-        <v>4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Solidago canadensis</t>
+          <t>Solidago nemoralis</t>
         </is>
       </c>
       <c r="B159">
-        <v>171</v>
+        <v>57</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Solidago juncea</t>
+          <t>Solidago rigida</t>
         </is>
       </c>
       <c r="B160">
-        <v>54</v>
+        <v>151</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Solidago nemoralis</t>
+          <t>Solidago speciosa</t>
         </is>
       </c>
       <c r="B161">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Solidago rigida</t>
+          <t>Sorghastrum nutans</t>
         </is>
       </c>
       <c r="B162">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Solidago speciosa</t>
+          <t>Sporobolus cryptandrus</t>
         </is>
       </c>
       <c r="B163">
-        <v>75</v>
+        <v>196</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sorghastrum nutans</t>
+          <t>Stellaria media</t>
         </is>
       </c>
       <c r="B164">
-        <v>158</v>
+        <v>115</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sporobolus cryptandrus</t>
+          <t>Symphyotrichum</t>
         </is>
       </c>
       <c r="B165">
-        <v>196</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Stellaria media</t>
+          <t>Symphyotrichum ericoides</t>
         </is>
       </c>
       <c r="B166">
-        <v>115</v>
+        <v>78</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Symphyotrichum</t>
+          <t>Symphyotrichum laeve</t>
         </is>
       </c>
       <c r="B167">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Symphyotrichum ericoides</t>
+          <t>Symphyotrichum lanceolatum</t>
         </is>
       </c>
       <c r="B168">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Symphyotrichum laeve</t>
+          <t>Symphyotrichum oolentangiense</t>
         </is>
       </c>
       <c r="B169">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Symphyotrichum lanceolatum</t>
+          <t>Symphyotrichum pilosum</t>
         </is>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>135</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Symphyotrichum oolentangiense</t>
+          <t>Symphyotrichum undulatum</t>
         </is>
       </c>
       <c r="B171">
-        <v>54</v>
+        <v>162</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Symphyotrichum pilosum</t>
+          <t>Taraxacum officinale</t>
         </is>
       </c>
       <c r="B172">
-        <v>135</v>
+        <v>39</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Symphyotrichum undulatum</t>
+          <t>Toxicodendron radicans</t>
         </is>
       </c>
       <c r="B173">
-        <v>162</v>
+        <v>29</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Taraxacum officinale</t>
+          <t>Tradescantia ohiensis</t>
         </is>
       </c>
       <c r="B174">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Toxicodendron radicans</t>
+          <t>Tragopogon</t>
         </is>
       </c>
       <c r="B175">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Tradescantia ohiensis</t>
+          <t>Trifolium</t>
         </is>
       </c>
       <c r="B176">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Tragopogon</t>
+          <t>Trifolium arvense</t>
         </is>
       </c>
       <c r="B177">
-        <v>26</v>
+        <v>91</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Trifolium</t>
+          <t>Trifolium campestre</t>
         </is>
       </c>
       <c r="B178">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Trifolium arvense</t>
+          <t>Trifolium dubium</t>
         </is>
       </c>
       <c r="B179">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Trifolium campestre</t>
+          <t>Trifolium hybridum</t>
         </is>
       </c>
       <c r="B180">
@@ -2159,175 +2159,155 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Trifolium dubium</t>
+          <t>Trifolium pratense</t>
         </is>
       </c>
       <c r="B181">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Trifolium hybridum</t>
+          <t>Trifolium repens</t>
         </is>
       </c>
       <c r="B182">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Trifolium pratense</t>
+          <t>Turritis glabra</t>
         </is>
       </c>
       <c r="B183">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Trifolium repens</t>
+          <t>Ulmus</t>
         </is>
       </c>
       <c r="B184">
-        <v>43</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Turritis glabra</t>
+          <t>Urtica dioica</t>
         </is>
       </c>
       <c r="B185">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Ulmus</t>
+          <t>Verbascum thapsus</t>
         </is>
       </c>
       <c r="B186">
-        <v>4</v>
+        <v>218</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Urtica dioica</t>
+          <t>Verbena</t>
         </is>
       </c>
       <c r="B187">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Verbascum thapsus</t>
+          <t>Verbena stricta</t>
         </is>
       </c>
       <c r="B188">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Verbena</t>
+          <t>Verbena urticifolia</t>
         </is>
       </c>
       <c r="B189">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Verbena stricta</t>
+          <t>Vicia</t>
         </is>
       </c>
       <c r="B190">
-        <v>230</v>
+        <v>137</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Verbena urticifolia</t>
+          <t>Vinca</t>
         </is>
       </c>
       <c r="B191">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Vicia</t>
+          <t>Viola</t>
         </is>
       </c>
       <c r="B192">
-        <v>137</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Vinca</t>
+          <t>Vitis</t>
         </is>
       </c>
       <c r="B193">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Viola</t>
+          <t>Zizia aptera</t>
         </is>
       </c>
       <c r="B194">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Vitis</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="B195">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Zizia aptera</t>
-        </is>
-      </c>
       <c r="B196">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="B197">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="B198">
         <v>92</v>
       </c>
     </row>
